--- a/Excel Class Files/Part 5 Conditional Functions.xlsx
+++ b/Excel Class Files/Part 5 Conditional Functions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Excel Class Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BBAEFD1-8469-4972-BC24-6A453533CB16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69311073-7E94-49A3-81DE-A30F58F710E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="147">
   <si>
     <t>Karan Sisodiya</t>
   </si>
@@ -527,6 +527,30 @@
   <si>
     <t>Ans</t>
   </si>
+  <si>
+    <t xml:space="preserve">You can get a bike only after you score above 80 Marks and a budget of above 5,00,000 </t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Budget</t>
+  </si>
+  <si>
+    <t>Bike</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate discount (12%) from sales when the quantity is above 10 and the profit is above 200 </t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>QTY</t>
+  </si>
+  <si>
+    <t>Dicount Amount</t>
+  </si>
 </sst>
 </file>
 
@@ -538,7 +562,7 @@
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0;[Red]\-&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -631,6 +655,15 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -755,7 +788,7 @@
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -798,17 +831,18 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -848,7 +882,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>733691</xdr:colOff>
+      <xdr:colOff>474988</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>101757</xdr:rowOff>
     </xdr:to>
@@ -1460,8 +1494,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{993E0ED4-0E58-4066-B01E-10510BC5FFAB}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="15.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" s="24" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
@@ -1518,6 +1555,64 @@
       <c r="A25" s="28" t="s">
         <v>111</v>
       </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="45" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>140</v>
+      </c>
+      <c r="B30">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>141</v>
+      </c>
+      <c r="B31" s="40">
+        <v>800000</v>
+      </c>
+      <c r="D31" t="s">
+        <v>142</v>
+      </c>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="45" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36">
+        <v>7800</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>144</v>
+      </c>
+      <c r="B37">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>145</v>
+      </c>
+      <c r="B38">
+        <v>12</v>
+      </c>
+      <c r="D38" t="s">
+        <v>146</v>
+      </c>
+      <c r="E38" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1671,12 +1766,12 @@
       <c r="C21" s="1"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="B25" s="38"/>
-      <c r="C25" s="38"/>
-      <c r="D25" s="38"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
       <c r="F25" s="26" t="s">
         <v>16</v>
       </c>
@@ -1696,10 +1791,10 @@
       <c r="D26" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="38"/>
+      <c r="G26" s="41"/>
       <c r="H26" s="16" t="s">
         <v>12</v>
       </c>
@@ -1713,10 +1808,10 @@
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="21"/>
-      <c r="F27" s="39" t="s">
+      <c r="F27" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="G27" s="39"/>
+      <c r="G27" s="42"/>
       <c r="H27" s="18">
         <v>0.05</v>
       </c>
@@ -1730,10 +1825,10 @@
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="6"/>
-      <c r="F28" s="40" t="s">
+      <c r="F28" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="G28" s="40"/>
+      <c r="G28" s="43"/>
       <c r="H28" s="3">
         <v>0.1</v>
       </c>
@@ -1747,10 +1842,10 @@
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="6"/>
-      <c r="F29" s="40" t="s">
+      <c r="F29" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="G29" s="40"/>
+      <c r="G29" s="43"/>
       <c r="H29" s="3">
         <v>0.2</v>
       </c>
@@ -2131,19 +2226,19 @@
       <c r="F4" s="26"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="42" t="s">
+      <c r="B5" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="42" t="s">
+      <c r="E5" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="42" t="s">
+      <c r="F5" s="38" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2283,16 +2378,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="32" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="41" t="s">
+      <c r="A1" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
     </row>
     <row r="2" spans="1:8" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
@@ -2513,25 +2608,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="C1" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="D1" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="43" t="s">
+      <c r="E1" s="39" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="G1" s="39" t="s">
         <v>121</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="39" t="s">
         <v>138</v>
       </c>
     </row>
@@ -2548,7 +2643,7 @@
       <c r="D2" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="40">
         <v>1000</v>
       </c>
       <c r="G2" t="s">
@@ -2568,7 +2663,7 @@
       <c r="D3" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="44">
+      <c r="E3" s="40">
         <v>800</v>
       </c>
       <c r="G3" t="s">
@@ -2589,7 +2684,7 @@
       <c r="D4" t="s">
         <v>81</v>
       </c>
-      <c r="E4" s="44">
+      <c r="E4" s="40">
         <v>650</v>
       </c>
       <c r="G4" t="s">
@@ -2610,7 +2705,7 @@
       <c r="D5" t="s">
         <v>76</v>
       </c>
-      <c r="E5" s="44">
+      <c r="E5" s="40">
         <v>850</v>
       </c>
     </row>
@@ -2627,7 +2722,7 @@
       <c r="D6" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="44">
+      <c r="E6" s="40">
         <v>1400</v>
       </c>
       <c r="G6" t="s">
@@ -2647,7 +2742,7 @@
       <c r="D7" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="44">
+      <c r="E7" s="40">
         <v>1000</v>
       </c>
       <c r="G7" t="s">
@@ -2667,7 +2762,7 @@
       <c r="D8" t="s">
         <v>78</v>
       </c>
-      <c r="E8" s="44">
+      <c r="E8" s="40">
         <v>1000</v>
       </c>
       <c r="G8" t="s">
@@ -2687,7 +2782,7 @@
       <c r="D9" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="44">
+      <c r="E9" s="40">
         <v>850</v>
       </c>
       <c r="G9" t="s">
@@ -2707,7 +2802,7 @@
       <c r="D10" t="s">
         <v>76</v>
       </c>
-      <c r="E10" s="44">
+      <c r="E10" s="40">
         <v>650</v>
       </c>
       <c r="G10" t="s">
@@ -2727,7 +2822,7 @@
       <c r="D11" t="s">
         <v>78</v>
       </c>
-      <c r="E11" s="44">
+      <c r="E11" s="40">
         <v>800</v>
       </c>
     </row>
@@ -2744,7 +2839,7 @@
       <c r="D12" t="s">
         <v>81</v>
       </c>
-      <c r="E12" s="44">
+      <c r="E12" s="40">
         <v>1400</v>
       </c>
     </row>
@@ -2761,7 +2856,7 @@
       <c r="D13" t="s">
         <v>78</v>
       </c>
-      <c r="E13" s="44">
+      <c r="E13" s="40">
         <v>650</v>
       </c>
     </row>
@@ -2778,7 +2873,7 @@
       <c r="D14" t="s">
         <v>81</v>
       </c>
-      <c r="E14" s="44">
+      <c r="E14" s="40">
         <v>800</v>
       </c>
     </row>
@@ -2795,7 +2890,7 @@
       <c r="D15" t="s">
         <v>76</v>
       </c>
-      <c r="E15" s="44">
+      <c r="E15" s="40">
         <v>1400</v>
       </c>
     </row>
@@ -2812,7 +2907,7 @@
       <c r="D16" t="s">
         <v>78</v>
       </c>
-      <c r="E16" s="44">
+      <c r="E16" s="40">
         <v>1400</v>
       </c>
     </row>

--- a/Excel Class Files/Part 5 Conditional Functions.xlsx
+++ b/Excel Class Files/Part 5 Conditional Functions.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\deves\Documents\GitHub\Free_Datasets\Excel Class Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69311073-7E94-49A3-81DE-A30F58F710E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A3F3C5-2AA7-4B38-A04D-3D18F4CFD408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IF" sheetId="8" r:id="rId1"/>
-    <sheet name="Nested IFs" sheetId="2" r:id="rId2"/>
-    <sheet name="IFS" sheetId="9" r:id="rId3"/>
+    <sheet name="IFS" sheetId="9" r:id="rId2"/>
+    <sheet name="Nested IFs" sheetId="2" r:id="rId3"/>
     <sheet name="Agg+ifs" sheetId="5" r:id="rId4"/>
     <sheet name="Practice" sheetId="4" r:id="rId5"/>
     <sheet name="Iferror" sheetId="11" r:id="rId6"/>
@@ -39,10 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="147">
-  <si>
-    <t>Karan Sisodiya</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="152">
   <si>
     <t>Piyush Lodhi</t>
   </si>
@@ -550,6 +547,24 @@
   </si>
   <si>
     <t>Dicount Amount</t>
+  </si>
+  <si>
+    <t>Kusum lodhi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You can participate in the sports if you have height above 6 feet and weight below 100 kg?  </t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Can play</t>
+  </si>
+  <si>
+    <t>Price</t>
   </si>
 </sst>
 </file>
@@ -836,13 +851,13 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -1494,7 +1509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{993E0ED4-0E58-4066-B01E-10510BC5FFAB}">
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultColWidth="12" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="15.85546875" customWidth="1"/>
@@ -1502,22 +1517,22 @@
   <sheetData>
     <row r="1" spans="1:2" s="24" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:2" s="24" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B15">
         <v>23</v>
@@ -1537,15 +1552,15 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E21" s="27" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22">
         <v>7800</v>
@@ -1553,17 +1568,17 @@
     </row>
     <row r="25" spans="1:5" s="29" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="45" t="s">
-        <v>139</v>
+      <c r="A28" s="41" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B30">
         <v>89</v>
@@ -1571,24 +1586,24 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B31" s="40">
         <v>800000</v>
       </c>
       <c r="D31" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="1"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="41" t="s">
         <v>142</v>
-      </c>
-      <c r="E31" s="1"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="45" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B36">
         <v>7800</v>
@@ -1596,7 +1611,7 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B37">
         <v>450</v>
@@ -1604,15 +1619,40 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B38">
         <v>12</v>
       </c>
       <c r="D38" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E38" s="1"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="41" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" s="26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B43">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="B44">
+        <v>89</v>
+      </c>
+      <c r="D44" t="s">
+        <v>150</v>
+      </c>
+      <c r="E44" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1621,6 +1661,160 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571C7BFA-0B40-4DB6-872D-F626EFD826E3}">
+  <dimension ref="A1:F14"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="24" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" s="31" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="30" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="26"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="4">
+        <v>35</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="E6" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1">
+        <v>60</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="E7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="1">
+        <v>92</v>
+      </c>
+      <c r="C8" s="1"/>
+      <c r="E8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="1">
+        <v>74</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="E9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1">
+        <v>85</v>
+      </c>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="1">
+        <v>48</v>
+      </c>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1">
+        <v>64</v>
+      </c>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="1">
+        <v>97</v>
+      </c>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="1">
+        <v>22</v>
+      </c>
+      <c r="C14" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6CBC569-0413-41F9-A8E2-F8D7E3108224}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A10:H68"/>
@@ -1636,111 +1830,111 @@
   <sheetData>
     <row r="10" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>35</v>
-      </c>
-      <c r="C12" s="16" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="4">
         <v>35</v>
       </c>
       <c r="C13" s="4"/>
       <c r="E13" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F13" s="26"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B14" s="1">
         <v>60</v>
       </c>
       <c r="C14" s="1"/>
       <c r="E14" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B15" s="1">
         <v>92</v>
       </c>
       <c r="C15" s="1"/>
       <c r="E15" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16" s="1">
         <v>74</v>
       </c>
       <c r="C16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" s="1">
         <v>85</v>
       </c>
       <c r="C17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="1">
         <v>48</v>
       </c>
       <c r="C18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B19" s="1">
         <v>64</v>
@@ -1749,7 +1943,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1">
         <v>97</v>
@@ -1758,7 +1952,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1">
         <v>22</v>
@@ -1766,93 +1960,93 @@
       <c r="C21" s="1"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="41" t="s">
-        <v>17</v>
-      </c>
-      <c r="B25" s="41"/>
-      <c r="C25" s="41"/>
-      <c r="D25" s="41"/>
+      <c r="A25" s="42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="42"/>
       <c r="F25" s="26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G25" s="26"/>
       <c r="H25" s="26"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B26" s="16" t="s">
+        <v>151</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="16" t="s">
+      <c r="F26" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" s="41" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="41"/>
+      <c r="G26" s="42"/>
       <c r="H26" s="16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" s="21">
         <v>9750</v>
       </c>
       <c r="C27" s="4"/>
       <c r="D27" s="21"/>
-      <c r="F27" s="42" t="s">
-        <v>10</v>
-      </c>
-      <c r="G27" s="42"/>
+      <c r="F27" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="43"/>
       <c r="H27" s="18">
         <v>0.05</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B28" s="6">
         <v>5159</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="6"/>
-      <c r="F28" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="G28" s="43"/>
+      <c r="F28" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="G28" s="44"/>
       <c r="H28" s="3">
         <v>0.1</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" s="6">
         <v>7774</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="6"/>
-      <c r="F29" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="G29" s="43"/>
+      <c r="F29" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="44"/>
       <c r="H29" s="3">
         <v>0.2</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B30" s="6">
         <v>6207</v>
@@ -1862,7 +2056,7 @@
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" s="6">
         <v>1980</v>
@@ -1873,7 +2067,7 @@
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B32" s="6">
         <v>4095</v>
@@ -1883,7 +2077,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B33" s="6">
         <v>2800</v>
@@ -1893,7 +2087,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B34" s="6">
         <v>4925</v>
@@ -1903,7 +2097,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>0</v>
+        <v>146</v>
       </c>
       <c r="B35" s="6">
         <v>5928</v>
@@ -1913,7 +2107,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B36" s="22">
         <f>SUM(B27:B35)</f>
@@ -1930,21 +2124,21 @@
     </row>
     <row r="39" spans="1:5" s="26" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D40" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -1953,10 +2147,10 @@
       </c>
       <c r="B41" s="4"/>
       <c r="D41" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
@@ -1965,10 +2159,10 @@
       </c>
       <c r="B42" s="1"/>
       <c r="D42" s="10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
@@ -1977,10 +2171,10 @@
       </c>
       <c r="B43" s="1"/>
       <c r="D43" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
@@ -2033,89 +2227,89 @@
     </row>
     <row r="55" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" s="23" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="17" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C56" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B57" s="21">
         <v>30</v>
       </c>
       <c r="C57" s="4"/>
       <c r="E57" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B58" s="6">
         <v>1880</v>
       </c>
       <c r="C58" s="1"/>
       <c r="E58" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B59" s="6">
         <v>821</v>
       </c>
       <c r="C59" s="1"/>
       <c r="E59" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>64</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B60" s="6">
         <v>450</v>
       </c>
       <c r="C60" s="1"/>
       <c r="E60" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B61" s="6">
         <v>1073</v>
@@ -2124,7 +2318,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B62" s="6">
         <v>500</v>
@@ -2133,7 +2327,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="10" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B63" s="6">
         <v>9000</v>
@@ -2142,7 +2336,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B64" s="6">
         <v>945</v>
@@ -2151,7 +2345,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B65" s="6">
         <v>320</v>
@@ -2160,7 +2354,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B66" s="6">
         <v>1233</v>
@@ -2169,7 +2363,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B67" s="6">
         <v>2560</v>
@@ -2178,7 +2372,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B68" s="6">
         <v>1965</v>
@@ -2195,160 +2389,6 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{571C7BFA-0B40-4DB6-872D-F626EFD826E3}">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="24" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" s="31" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="26"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="38" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="4">
-        <v>35</v>
-      </c>
-      <c r="C6" s="4"/>
-      <c r="E6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="1">
-        <v>60</v>
-      </c>
-      <c r="C7" s="1"/>
-      <c r="E7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="1">
-        <v>92</v>
-      </c>
-      <c r="C8" s="1"/>
-      <c r="E8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="1">
-        <v>74</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="E9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="1">
-        <v>85</v>
-      </c>
-      <c r="C10" s="1"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="1">
-        <v>48</v>
-      </c>
-      <c r="C11" s="1"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1">
-        <v>64</v>
-      </c>
-      <c r="C12" s="1"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1">
-        <v>97</v>
-      </c>
-      <c r="C13" s="1"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B14" s="1">
-        <v>22</v>
-      </c>
-      <c r="C14" s="1"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2378,34 +2418,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="32" customFormat="1" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
+      <c r="A1" s="45" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
     </row>
     <row r="2" spans="1:8" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" s="33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B2" s="29"/>
       <c r="F2" s="34"/>
     </row>
     <row r="3" spans="1:8" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B3" s="29"/>
       <c r="F3" s="34"/>
     </row>
     <row r="4" spans="1:8" s="32" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" s="33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B4" s="29"/>
       <c r="F4" s="34"/>
@@ -2415,20 +2455,20 @@
     </row>
     <row r="6" spans="1:8" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" s="35" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6"/>
       <c r="F6" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="11" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
@@ -2436,17 +2476,17 @@
         <v>42075</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D7">
         <v>203</v>
       </c>
       <c r="E7"/>
       <c r="F7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -2454,16 +2494,16 @@
         <v>42087</v>
       </c>
       <c r="B8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D8">
         <v>240</v>
       </c>
       <c r="F8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -2471,16 +2511,16 @@
         <v>42099</v>
       </c>
       <c r="B9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D9">
         <v>120</v>
       </c>
       <c r="F9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -2488,16 +2528,16 @@
         <v>42111</v>
       </c>
       <c r="B10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D10">
         <v>90</v>
       </c>
       <c r="F10" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -2505,16 +2545,16 @@
         <v>42123</v>
       </c>
       <c r="B11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C11" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D11">
         <v>45</v>
       </c>
       <c r="F11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -2522,16 +2562,16 @@
         <v>42135</v>
       </c>
       <c r="B12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C12" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D12">
         <v>38</v>
       </c>
       <c r="F12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -2539,16 +2579,16 @@
         <v>42147</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13">
         <v>90</v>
       </c>
       <c r="F13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -2556,16 +2596,16 @@
         <v>42159</v>
       </c>
       <c r="B14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D14">
         <v>24</v>
       </c>
       <c r="F14" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -2573,16 +2613,16 @@
         <v>42171</v>
       </c>
       <c r="B15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D15">
         <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2609,101 +2649,101 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="39" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B1" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="D1" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="E1" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="39" t="s">
-        <v>72</v>
-      </c>
       <c r="G1" s="39" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H1" s="39" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s">
         <v>73</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>74</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>75</v>
-      </c>
-      <c r="D2" t="s">
-        <v>76</v>
       </c>
       <c r="E2" s="40">
         <v>1000</v>
       </c>
       <c r="G2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B3" t="s">
         <v>73</v>
       </c>
-      <c r="B3" t="s">
-        <v>74</v>
-      </c>
       <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
         <v>77</v>
-      </c>
-      <c r="D3" t="s">
-        <v>78</v>
       </c>
       <c r="E3" s="40">
         <v>800</v>
       </c>
       <c r="G3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B4" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" t="s">
         <v>79</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>80</v>
-      </c>
-      <c r="D4" t="s">
-        <v>81</v>
       </c>
       <c r="E4" s="40">
         <v>650</v>
       </c>
       <c r="G4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E5" s="40">
         <v>850</v>
@@ -2711,116 +2751,116 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E6" s="40">
         <v>1400</v>
       </c>
       <c r="G6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
         <v>73</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>74</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>75</v>
-      </c>
-      <c r="D7" t="s">
-        <v>76</v>
       </c>
       <c r="E7" s="40">
         <v>1000</v>
       </c>
       <c r="G7" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
         <v>73</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>74</v>
       </c>
-      <c r="C8" t="s">
-        <v>75</v>
-      </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E8" s="40">
         <v>1000</v>
       </c>
       <c r="G8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E9" s="40">
         <v>850</v>
       </c>
       <c r="G9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C10" t="s">
         <v>79</v>
       </c>
-      <c r="C10" t="s">
-        <v>80</v>
-      </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" s="40">
         <v>650</v>
       </c>
       <c r="G10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
         <v>77</v>
-      </c>
-      <c r="D11" t="s">
-        <v>78</v>
       </c>
       <c r="E11" s="40">
         <v>800</v>
@@ -2828,16 +2868,16 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D12" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E12" s="40">
         <v>1400</v>
@@ -2845,16 +2885,16 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C13" t="s">
         <v>79</v>
       </c>
-      <c r="C13" t="s">
-        <v>80</v>
-      </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" s="40">
         <v>650</v>
@@ -2862,16 +2902,16 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E14" s="40">
         <v>800</v>
@@ -2879,16 +2919,16 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E15" s="40">
         <v>1400</v>
@@ -2896,16 +2936,16 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" s="40">
         <v>1400</v>
@@ -2913,26 +2953,26 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="C23" s="5" t="s">
         <v>90</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C24" s="15">
         <v>12000</v>
@@ -2940,10 +2980,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="C25" s="15">
         <v>15000</v>
@@ -2951,10 +2991,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C26" s="15">
         <v>9500</v>
@@ -2962,10 +3002,10 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C27" s="15">
         <v>18000</v>
@@ -2973,10 +3013,10 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C28" s="15">
         <v>22000</v>
@@ -2984,40 +3024,40 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>92</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>93</v>
       </c>
       <c r="C29" s="15">
         <v>10500</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F29" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C30" s="15">
         <v>16000</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C31" s="15">
         <v>14500</v>
@@ -3036,13 +3076,13 @@
   <sheetData>
     <row r="1" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B1" s="37"/>
     </row>
     <row r="2" spans="1:2" s="29" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
